--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487713_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487713_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4729</v>
+        <v>4.5424</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6617</v>
+        <v>6.6222</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1888</v>
+        <v>-2.0798</v>
       </c>
       <c r="G2" t="n">
         <v>1.466</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0126</v>
+        <v>0.0569</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2557</v>
+        <v>0.2162</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2683</v>
+        <v>-0.1592</v>
       </c>
       <c r="V2" t="n">
         <v>2.8254</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0051</v>
+        <v>2.0522</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1137</v>
+        <v>3.3184</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.1086</v>
+        <v>-1.2662</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2404</v>
+        <v>2.0524</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6665</v>
+        <v>-0.5396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5739</v>
+        <v>2.5921</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9864</v>
+        <v>4.369</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3604</v>
+        <v>1.2152</v>
       </c>
       <c r="L3" t="n">
-        <v>2.626</v>
+        <v>3.1538</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.746</v>
+        <v>-2.3166</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6939</v>
+        <v>-1.7549</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0521</v>
+        <v>-0.5617</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1527</v>
+        <v>-0.3003</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5616</v>
+        <v>0.1135</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4089</v>
+        <v>-0.4138</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.2821</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.506</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6735</v>
+        <v>1.0702</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1577</v>
+        <v>5.5331</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4842</v>
+        <v>-4.4629</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0524</v>
+        <v>1.2404</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5396</v>
+        <v>0.6665</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5921</v>
+        <v>0.5739</v>
       </c>
       <c r="J4" t="n">
-        <v>4.369</v>
+        <v>4.9864</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2152</v>
+        <v>2.3604</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1538</v>
+        <v>2.626</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3166</v>
+        <v>-3.746</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7549</v>
+        <v>-1.6939</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5617</v>
+        <v>-2.0521</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.679</v>
+        <v>0.2179</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0471</v>
+        <v>0.9811</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6319</v>
+        <v>-0.7632</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6831</v>
+        <v>0.7014</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0799</v>
+        <v>0.0202</v>
       </c>
       <c r="F5" t="n">
-        <v>0.763</v>
+        <v>0.6813</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1038</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1272</v>
+        <v>0.1455</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2483</v>
+        <v>0.1666</v>
       </c>
       <c r="V5" t="n">
         <v>0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2866</v>
+        <v>-0.5386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.873</v>
+        <v>0.5937</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1596</v>
+        <v>-1.1323</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1529</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4186</v>
+        <v>0.1666</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5473</v>
+        <v>0.268</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1287</v>
+        <v>-0.1015</v>
       </c>
       <c r="V6" t="n">
         <v>1.2239</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0227</v>
+        <v>-0.9954</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9288999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0665</v>
       </c>
       <c r="G7" t="n">
         <v>0.09030000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1882</v>
+        <v>-0.1609</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1579</v>
+        <v>-3.3036</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9043</v>
+        <v>-1.1045</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2535</v>
+        <v>-2.199</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3324</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.2428</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3039</v>
+        <v>0.1037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4011</v>
+        <v>-0.3465</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5642</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1525</v>
+        <v>-3.9546</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7635</v>
+        <v>-4.1023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.611</v>
+        <v>0.1477</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2656</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3347</v>
+        <v>-0.1368</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7874</v>
+        <v>-0.1262</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4527</v>
+        <v>-0.0106</v>
       </c>
       <c r="V9" t="n">
         <v>0.6119</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.488</v>
+        <v>-4.8462</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.406</v>
+        <v>-1.5544</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.082</v>
+        <v>-3.2918</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7882</v>
+        <v>-1.4445</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5998</v>
+        <v>2.3554</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1884</v>
+        <v>-3.7999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0818</v>
+        <v>1.9948</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0412</v>
+        <v>3.8928</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>-1.898</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.87</v>
+        <v>-3.4393</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.641</v>
+        <v>-1.5374</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.229</v>
+        <v>-1.9019</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-3.8806</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.758</v>
+        <v>-0.2972</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>0.0493</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1523</v>
+        <v>-0.3465</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1657</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0.2821</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4477</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5797</v>
+        <v>-4.9998</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0154</v>
+        <v>-0.945</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5643</v>
+        <v>-4.0547</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4445</v>
+        <v>-1.7882</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3554</v>
+        <v>-0.5998</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7999</v>
+        <v>-1.1884</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9948</v>
+        <v>0.0818</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8928</v>
+        <v>0.0412</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.898</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.4393</v>
+        <v>-1.87</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5374</v>
+        <v>-0.641</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9019</v>
+        <v>-1.229</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1045</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8806</v>
+        <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0307</v>
+        <v>-0.2697</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4116</v>
+        <v>-0.1447</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6191</v>
+        <v>-0.125</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W11" t="n">
         <v>0.2821</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2821</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6004</v>
+        <v>-5.5755</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6225</v>
+        <v>-1.7611</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9779</v>
+        <v>-3.8144</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6082</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9042</v>
+        <v>-0.8793</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9567</v>
+        <v>-0.0954</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9475</v>
+        <v>-0.7839</v>
       </c>
       <c r="V12" t="n">
         <v>-1.506</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.4532</v>
+        <v>-15.8475</v>
       </c>
       <c r="E13" t="n">
-        <v>5.085599999999999</v>
+        <v>5.691400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.5387</v>
+        <v>-21.5386</v>
       </c>
       <c r="G13" t="n">
         <v>-6.8465</v>
@@ -1444,7 +1444,7 @@
         <v>14.0866</v>
       </c>
       <c r="K13" t="n">
-        <v>9.8041</v>
+        <v>9.804099999999998</v>
       </c>
       <c r="L13" t="n">
         <v>4.282500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.6719</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3666</v>
+        <v>-1.7607</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6782999999999998</v>
+        <v>1.2839</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.045</v>
+        <v>-3.0445</v>
       </c>
       <c r="V13" t="n">
         <v>0.5207999999999997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1625</v>
+        <v>10.787</v>
       </c>
       <c r="E14" t="n">
-        <v>9.428699999999999</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7338</v>
+        <v>1.058</v>
       </c>
       <c r="G14" t="n">
         <v>7.4087</v>
@@ -1546,13 +1546,13 @@
         <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.576</v>
+        <v>0.0485</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0011</v>
+        <v>0.3014</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.2529</v>
       </c>
       <c r="V14" t="n">
         <v>2.1657</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2353</v>
+        <v>6.1963</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7768</v>
+        <v>6.2773</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5415</v>
+        <v>-0.081</v>
       </c>
       <c r="G15" t="n">
         <v>2.0734</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8486</v>
+        <v>0.1124</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0595</v>
+        <v>0.441</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7891</v>
+        <v>-0.3286</v>
       </c>
       <c r="V15" t="n">
         <v>2.0701</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4103</v>
+        <v>4.1378</v>
       </c>
       <c r="E16" t="n">
         <v>4.7251</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3147</v>
+        <v>-0.5873</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2598</v>
@@ -1702,13 +1702,13 @@
         <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9702</v>
+        <v>0.6976</v>
       </c>
       <c r="T16" t="n">
         <v>0.5473</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4229</v>
+        <v>0.1503</v>
       </c>
       <c r="V16" t="n">
         <v>3.9537</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5047</v>
+        <v>2.8585</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3171</v>
+        <v>3.6164</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8124</v>
+        <v>-0.7579</v>
       </c>
       <c r="G17" t="n">
         <v>2.2635</v>
@@ -1780,13 +1780,13 @@
         <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6308</v>
+        <v>-0.0154</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.2706</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3405</v>
+        <v>-0.286</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9418</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0444</v>
+        <v>2.5449</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4518</v>
+        <v>2.9523</v>
       </c>
       <c r="F18" t="n">
         <v>-0.4074</v>
@@ -1858,10 +1858,10 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5821</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5451</v>
+        <v>-0.0446</v>
       </c>
       <c r="U18" t="n">
         <v>-0.037</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4873</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6367</v>
+        <v>0.7192</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1241</v>
+        <v>-0.0776</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8002</v>
+        <v>-1.1724</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3002</v>
+        <v>1.7868</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9881</v>
+        <v>0.9825</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2317</v>
+        <v>-0.276</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2436</v>
+        <v>1.2585</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4881</v>
+        <v>-0.3681</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5685</v>
+        <v>-0.8964</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0566</v>
+        <v>0.5283</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0366</v>
+        <v>-0.3609</v>
       </c>
       <c r="T19" t="n">
-        <v>0.729</v>
+        <v>-0.2633</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3076</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6015</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4081</v>
+        <v>0.0752</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6191</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.211</v>
+        <v>1.0122</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6143999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1724</v>
+        <v>-1.8002</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7868</v>
+        <v>1.3002</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9825</v>
+        <v>-0.9881</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.276</v>
+        <v>-1.2317</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2585</v>
+        <v>0.2436</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3681</v>
+        <v>0.4881</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8964</v>
+        <v>-0.5685</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5283</v>
+        <v>1.0566</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5944</v>
+        <v>0.6244</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3634</v>
+        <v>0.4287</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.231</v>
+        <v>0.1957</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.6015</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1903</v>
+        <v>-0.9959</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0557</v>
+        <v>-1.4571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.246</v>
+        <v>0.4613</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6921</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5421</v>
+        <v>1.356</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5493</v>
+        <v>1.1479</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0072</v>
+        <v>0.2081</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6597</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4399</v>
+        <v>-2.3304</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4125</v>
+        <v>0.7128</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8524</v>
+        <v>-3.0432</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1379</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0184</v>
+        <v>0.0911</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3634</v>
+        <v>-0.0631</v>
       </c>
       <c r="U22" t="n">
-        <v>0.345</v>
+        <v>0.1542</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8332</v>
+        <v>-2.9149</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5886</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2446</v>
+        <v>-0.3264</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1062</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6611</v>
+        <v>0.5793</v>
       </c>
       <c r="T23" t="n">
         <v>0.4867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1743</v>
+        <v>0.0926</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7167</v>
+        <v>-3.8797</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9114</v>
+        <v>-2.2107</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8053</v>
+        <v>-1.669</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2202</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8546</v>
+        <v>-0.0177</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9085</v>
+        <v>-0.2078</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0538</v>
+        <v>0.1901</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8358</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.4531</v>
+        <v>17.1204</v>
       </c>
       <c r="E25" t="n">
         <v>21.5387</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.0854</v>
+        <v>-4.4183</v>
       </c>
       <c r="G25" t="n">
-        <v>6.846499999999999</v>
+        <v>6.846500000000001</v>
       </c>
       <c r="H25" t="n">
         <v>1.5076</v>
       </c>
       <c r="I25" t="n">
-        <v>5.338699999999999</v>
+        <v>5.338700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>20.9329</v>
@@ -2404,13 +2404,13 @@
         <v>18.4332</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3667</v>
+        <v>3.0337</v>
       </c>
       <c r="T25" t="n">
         <v>3.0448</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6783000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5208999999999999</v>
